--- a/0_Document/内部設計/parts/画面設計.xlsx
+++ b/0_Document/内部設計/parts/画面設計.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="Polaris Office Sheet" lastEdited="4" lowestEdited="4" rupBuild="10.115.191.55897"/>
   <workbookPr/>
   <bookViews>
-    <workbookView xWindow="360" yWindow="30" windowWidth="25755" windowHeight="11595" tabRatio="570" activeTab="0"/>
+    <workbookView xWindow="360" yWindow="30" windowWidth="25755" windowHeight="11595" tabRatio="560" activeTab="0"/>
   </bookViews>
   <sheets>
     <sheet name="front" sheetId="1" r:id="rId1"/>
@@ -140,7 +140,7 @@
       <color rgb="FFFFFFFF"/>
     </font>
   </fonts>
-  <fills count="36">
+  <fills count="35">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -348,12 +348,6 @@
         <bgColor rgb="FF000000"/>
       </patternFill>
     </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="0"/>
-        <bgColor rgb="FF000000"/>
-      </patternFill>
-    </fill>
   </fills>
   <borders count="10">
     <border>
@@ -610,7 +604,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -618,9 +612,6 @@
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="34" borderId="0" xfId="0" applyFill="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="35" borderId="0" xfId="0" applyFill="1">
       <alignment vertical="center"/>
     </xf>
   </cellXfs>
@@ -689,9 +680,9 @@
     </xdr:from>
     <xdr:to>
       <xdr:col>15</xdr:col>
-      <xdr:colOff>63500</xdr:colOff>
-      <xdr:row>47</xdr:row>
-      <xdr:rowOff>116205</xdr:rowOff>
+      <xdr:colOff>31750</xdr:colOff>
+      <xdr:row>39</xdr:row>
+      <xdr:rowOff>10795</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -708,7 +699,7 @@
             </a:ext>
           </a:extLst>
         </a:blip>
-        <a:srcRect t="10279" b="9137"/>
+        <a:srcRect t="9915" b="26118"/>
         <a:stretch>
           <a:fillRect/>
         </a:stretch>
@@ -716,7 +707,7 @@
       <xdr:spPr>
         <a:xfrm>
           <a:off x="339090" y="181610"/>
-          <a:ext cx="9990455" cy="7084060"/>
+          <a:ext cx="9958705" cy="5759450"/>
         </a:xfrm>
         <a:prstGeom prst="rect"/>
         <a:noFill/>
@@ -739,7 +730,7 @@
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="22" name="図 22"/>
+        <xdr:cNvPr id="22" name="図 22" descr="xl/media/OImage2934776731.png"/>
         <xdr:cNvPicPr>
           <a:picLocks noChangeAspect="1"/>
         </xdr:cNvPicPr>
@@ -801,7 +792,7 @@
               <a:alpha val="100000"/>
             </a:schemeClr>
           </a:solidFill>
-          <a:prstDash val="dot"/>
+          <a:prstDash val="sysDot"/>
           <a:miter lim="800000"/>
         </a:ln>
       </xdr:spPr>
@@ -857,7 +848,7 @@
               <a:alpha val="100000"/>
             </a:schemeClr>
           </a:solidFill>
-          <a:prstDash val="dot"/>
+          <a:prstDash val="sysDot"/>
           <a:miter lim="800000"/>
         </a:ln>
       </xdr:spPr>
@@ -913,7 +904,7 @@
               <a:alpha val="100000"/>
             </a:schemeClr>
           </a:solidFill>
-          <a:prstDash val="dot"/>
+          <a:prstDash val="sysDot"/>
           <a:miter lim="800000"/>
         </a:ln>
       </xdr:spPr>
@@ -969,7 +960,7 @@
               <a:alpha val="100000"/>
             </a:schemeClr>
           </a:solidFill>
-          <a:prstDash val="dot"/>
+          <a:prstDash val="sysDot"/>
           <a:miter lim="800000"/>
         </a:ln>
       </xdr:spPr>
@@ -990,6 +981,50 @@
         </a:fontRef>
       </xdr:style>
     </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>0</xdr:col>
+      <xdr:colOff>360045</xdr:colOff>
+      <xdr:row>32</xdr:row>
+      <xdr:rowOff>20955</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>15</xdr:col>
+      <xdr:colOff>31750</xdr:colOff>
+      <xdr:row>41</xdr:row>
+      <xdr:rowOff>127000</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="23" name="図 23"/>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId3" cstate="print">
+          <a:extLst>
+            <a:ext uri="{28A0092B-C50C-407E-A947-70E740481C1C}">
+              <a14:useLocalDpi xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" val="0"/>
+            </a:ext>
+          </a:extLst>
+        </a:blip>
+        <a:srcRect/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="339090" y="4884420"/>
+          <a:ext cx="9958705" cy="1477645"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect"/>
+        <a:noFill/>
+      </xdr:spPr>
+    </xdr:pic>
     <xdr:clientData/>
   </xdr:twoCellAnchor>
   <xdr:twoCellAnchor>
@@ -1341,7 +1376,7 @@
               <a:alpha val="100000"/>
             </a:schemeClr>
           </a:solidFill>
-          <a:prstDash val="dot"/>
+          <a:prstDash val="sysDot"/>
           <a:miter lim="800000"/>
         </a:ln>
       </xdr:spPr>
@@ -1367,13 +1402,13 @@
   <xdr:twoCellAnchor>
     <xdr:from>
       <xdr:col>0</xdr:col>
-      <xdr:colOff>666750</xdr:colOff>
+      <xdr:colOff>518795</xdr:colOff>
       <xdr:row>38</xdr:row>
       <xdr:rowOff>74295</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>1</xdr:col>
-      <xdr:colOff>487045</xdr:colOff>
+      <xdr:colOff>338455</xdr:colOff>
       <xdr:row>40</xdr:row>
       <xdr:rowOff>116205</xdr:rowOff>
     </xdr:to>
@@ -1386,8 +1421,8 @@
       </xdr:nvSpPr>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="645795" y="5852160"/>
-          <a:ext cx="506095" cy="346710"/>
+          <a:off x="497840" y="5852160"/>
+          <a:ext cx="505460" cy="346710"/>
         </a:xfrm>
         <a:prstGeom prst="rect"/>
         <a:noFill/>
@@ -1397,7 +1432,7 @@
               <a:alpha val="100000"/>
             </a:schemeClr>
           </a:solidFill>
-          <a:prstDash val="dot"/>
+          <a:prstDash val="sysDot"/>
           <a:miter lim="800000"/>
         </a:ln>
       </xdr:spPr>
@@ -1422,14 +1457,14 @@
   </xdr:twoCellAnchor>
   <xdr:twoCellAnchor>
     <xdr:from>
-      <xdr:col>3</xdr:col>
-      <xdr:colOff>328295</xdr:colOff>
+      <xdr:col>4</xdr:col>
+      <xdr:colOff>158750</xdr:colOff>
       <xdr:row>38</xdr:row>
       <xdr:rowOff>42545</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>4</xdr:col>
-      <xdr:colOff>360045</xdr:colOff>
+      <xdr:col>5</xdr:col>
+      <xdr:colOff>190500</xdr:colOff>
       <xdr:row>40</xdr:row>
       <xdr:rowOff>84455</xdr:rowOff>
     </xdr:to>
@@ -1442,7 +1477,7 @@
       </xdr:nvSpPr>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="2364740" y="5820410"/>
+          <a:off x="2880995" y="5820410"/>
           <a:ext cx="717550" cy="346710"/>
         </a:xfrm>
         <a:prstGeom prst="rect"/>
@@ -1453,7 +1488,7 @@
               <a:alpha val="100000"/>
             </a:schemeClr>
           </a:solidFill>
-          <a:prstDash val="dot"/>
+          <a:prstDash val="sysDot"/>
           <a:miter lim="800000"/>
         </a:ln>
       </xdr:spPr>
@@ -1478,14 +1513,14 @@
   </xdr:twoCellAnchor>
   <xdr:twoCellAnchor>
     <xdr:from>
-      <xdr:col>7</xdr:col>
-      <xdr:colOff>116205</xdr:colOff>
+      <xdr:col>9</xdr:col>
+      <xdr:colOff>296545</xdr:colOff>
       <xdr:row>38</xdr:row>
       <xdr:rowOff>63500</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>8</xdr:col>
-      <xdr:colOff>147955</xdr:colOff>
+      <xdr:col>10</xdr:col>
+      <xdr:colOff>328295</xdr:colOff>
       <xdr:row>40</xdr:row>
       <xdr:rowOff>106045</xdr:rowOff>
     </xdr:to>
@@ -1498,7 +1533,7 @@
       </xdr:nvSpPr>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="4895850" y="5841365"/>
+          <a:off x="6447790" y="5841365"/>
           <a:ext cx="717550" cy="347345"/>
         </a:xfrm>
         <a:prstGeom prst="rect"/>
@@ -1509,7 +1544,7 @@
               <a:alpha val="100000"/>
             </a:schemeClr>
           </a:solidFill>
-          <a:prstDash val="dot"/>
+          <a:prstDash val="sysDot"/>
           <a:miter lim="800000"/>
         </a:ln>
       </xdr:spPr>
@@ -1534,70 +1569,14 @@
   </xdr:twoCellAnchor>
   <xdr:twoCellAnchor>
     <xdr:from>
-      <xdr:col>10</xdr:col>
-      <xdr:colOff>635000</xdr:colOff>
-      <xdr:row>38</xdr:row>
-      <xdr:rowOff>42545</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>11</xdr:col>
-      <xdr:colOff>666750</xdr:colOff>
-      <xdr:row>40</xdr:row>
-      <xdr:rowOff>84455</xdr:rowOff>
-    </xdr:to>
-    <xdr:sp>
-      <xdr:nvSpPr>
-        <xdr:cNvPr id="14" name="図形 14"/>
-        <xdr:cNvSpPr>
-          <a:spLocks/>
-        </xdr:cNvSpPr>
-      </xdr:nvSpPr>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="7472045" y="5820410"/>
-          <a:ext cx="717550" cy="346710"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect"/>
-        <a:noFill/>
-        <a:ln w="19050" cap="flat" cmpd="sng">
-          <a:solidFill>
-            <a:schemeClr val="accent4">
-              <a:alpha val="100000"/>
-            </a:schemeClr>
-          </a:solidFill>
-          <a:prstDash val="dot"/>
-          <a:miter lim="800000"/>
-        </a:ln>
-      </xdr:spPr>
-      <xdr:style>
-        <a:lnRef idx="2">
-          <a:schemeClr val="accent1">
-            <a:shade val="50000"/>
-          </a:schemeClr>
-        </a:lnRef>
-        <a:fillRef idx="1">
-          <a:schemeClr val="accent1"/>
-        </a:fillRef>
-        <a:effectRef idx="0">
-          <a:schemeClr val="accent1"/>
-        </a:effectRef>
-        <a:fontRef idx="minor">
-          <a:schemeClr val="lt1"/>
-        </a:fontRef>
-      </xdr:style>
-    </xdr:sp>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor>
-    <xdr:from>
       <xdr:col>1</xdr:col>
-      <xdr:colOff>508000</xdr:colOff>
+      <xdr:colOff>360045</xdr:colOff>
       <xdr:row>38</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>2</xdr:col>
-      <xdr:colOff>296545</xdr:colOff>
+      <xdr:colOff>147955</xdr:colOff>
       <xdr:row>40</xdr:row>
       <xdr:rowOff>10795</xdr:rowOff>
     </xdr:to>
@@ -1610,8 +1589,8 @@
       </xdr:nvSpPr>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="1172845" y="5777865"/>
-          <a:ext cx="474345" cy="315595"/>
+          <a:off x="1024890" y="5777865"/>
+          <a:ext cx="473710" cy="315595"/>
         </a:xfrm>
         <a:prstGeom prst="rect"/>
         <a:noFill/>
@@ -1669,14 +1648,14 @@
   </xdr:twoCellAnchor>
   <xdr:twoCellAnchor>
     <xdr:from>
-      <xdr:col>4</xdr:col>
-      <xdr:colOff>360045</xdr:colOff>
+      <xdr:col>5</xdr:col>
+      <xdr:colOff>190500</xdr:colOff>
       <xdr:row>37</xdr:row>
       <xdr:rowOff>106045</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>5</xdr:col>
-      <xdr:colOff>147955</xdr:colOff>
+      <xdr:colOff>666750</xdr:colOff>
       <xdr:row>39</xdr:row>
       <xdr:rowOff>116205</xdr:rowOff>
     </xdr:to>
@@ -1689,8 +1668,8 @@
       </xdr:nvSpPr>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="3082290" y="5731510"/>
-          <a:ext cx="473710" cy="314960"/>
+          <a:off x="3598545" y="5731510"/>
+          <a:ext cx="476250" cy="314960"/>
         </a:xfrm>
         <a:prstGeom prst="rect"/>
         <a:noFill/>
@@ -1748,14 +1727,14 @@
   </xdr:twoCellAnchor>
   <xdr:twoCellAnchor>
     <xdr:from>
-      <xdr:col>8</xdr:col>
-      <xdr:colOff>158750</xdr:colOff>
+      <xdr:col>10</xdr:col>
+      <xdr:colOff>338455</xdr:colOff>
       <xdr:row>37</xdr:row>
       <xdr:rowOff>74295</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>8</xdr:col>
-      <xdr:colOff>635000</xdr:colOff>
+      <xdr:col>11</xdr:col>
+      <xdr:colOff>127000</xdr:colOff>
       <xdr:row>39</xdr:row>
       <xdr:rowOff>84455</xdr:rowOff>
     </xdr:to>
@@ -1768,8 +1747,8 @@
       </xdr:nvSpPr>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="5624195" y="5699760"/>
-          <a:ext cx="476250" cy="314960"/>
+          <a:off x="7175500" y="5699760"/>
+          <a:ext cx="474345" cy="314960"/>
         </a:xfrm>
         <a:prstGeom prst="rect"/>
         <a:noFill/>
@@ -1827,85 +1806,6 @@
   </xdr:twoCellAnchor>
   <xdr:twoCellAnchor>
     <xdr:from>
-      <xdr:col>11</xdr:col>
-      <xdr:colOff>666750</xdr:colOff>
-      <xdr:row>37</xdr:row>
-      <xdr:rowOff>74295</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>12</xdr:col>
-      <xdr:colOff>465455</xdr:colOff>
-      <xdr:row>39</xdr:row>
-      <xdr:rowOff>84455</xdr:rowOff>
-    </xdr:to>
-    <xdr:sp>
-      <xdr:nvSpPr>
-        <xdr:cNvPr id="18" name="テキストボックス 18"/>
-        <xdr:cNvSpPr txBox="1">
-          <a:spLocks/>
-        </xdr:cNvSpPr>
-      </xdr:nvSpPr>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="8189595" y="5699760"/>
-          <a:ext cx="484505" cy="314960"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect"/>
-        <a:noFill/>
-        <a:ln w="12700" cap="flat" cmpd="sng">
-          <a:solidFill>
-            <a:schemeClr val="accent4">
-              <a:alpha val="100000"/>
-            </a:schemeClr>
-          </a:solidFill>
-          <a:prstDash val="solid"/>
-          <a:miter lim="800000"/>
-        </a:ln>
-      </xdr:spPr>
-      <xdr:style>
-        <a:lnRef idx="2">
-          <a:schemeClr val="dk1"/>
-        </a:lnRef>
-        <a:fillRef idx="1">
-          <a:schemeClr val="lt1"/>
-        </a:fillRef>
-        <a:effectRef idx="0">
-          <a:schemeClr val="dk1"/>
-        </a:effectRef>
-        <a:fontRef idx="minor">
-          <a:schemeClr val="dk1"/>
-        </a:fontRef>
-      </xdr:style>
-      <xdr:txBody>
-        <a:bodyPr wrap="square" lIns="89535" tIns="46355" rIns="89535" bIns="46355" anchor="t" vertOverflow="clip" horzOverflow="clip">
-          <a:noAutofit/>
-        </a:bodyPr>
-        <a:p>
-          <a:pPr algn="l"/>
-          <a:r>
-            <a:rPr lang="ko-KR" altLang="en-US" sz="1000" kern="1200">
-              <a:solidFill>
-                <a:schemeClr val="dk1"/>
-              </a:solidFill>
-              <a:latin typeface="メイリオ"/>
-              <a:ea typeface="メイリオ"/>
-            </a:rPr>
-            <a:t>5-5</a:t>
-          </a:r>
-          <a:endParaRPr lang="ko-KR" altLang="en-US" sz="1000" kern="1200">
-            <a:solidFill>
-              <a:schemeClr val="dk1"/>
-            </a:solidFill>
-            <a:latin typeface="メイリオ"/>
-            <a:ea typeface="メイリオ"/>
-          </a:endParaRPr>
-        </a:p>
-      </xdr:txBody>
-    </xdr:sp>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor>
-    <xdr:from>
       <xdr:col>14</xdr:col>
       <xdr:colOff>338455</xdr:colOff>
       <xdr:row>30</xdr:row>
@@ -1986,13 +1886,13 @@
   <xdr:twoCellAnchor>
     <xdr:from>
       <xdr:col>1</xdr:col>
-      <xdr:colOff>423545</xdr:colOff>
+      <xdr:colOff>274955</xdr:colOff>
       <xdr:row>33</xdr:row>
       <xdr:rowOff>42545</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>2</xdr:col>
-      <xdr:colOff>635000</xdr:colOff>
+      <xdr:colOff>487045</xdr:colOff>
       <xdr:row>35</xdr:row>
       <xdr:rowOff>106045</xdr:rowOff>
     </xdr:to>
@@ -2005,8 +1905,8 @@
       </xdr:nvSpPr>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="1088390" y="5058410"/>
-          <a:ext cx="897255" cy="368300"/>
+          <a:off x="939800" y="5058410"/>
+          <a:ext cx="897890" cy="368300"/>
         </a:xfrm>
         <a:prstGeom prst="rect"/>
         <a:noFill/>
@@ -2016,7 +1916,7 @@
               <a:alpha val="100000"/>
             </a:schemeClr>
           </a:solidFill>
-          <a:prstDash val="dot"/>
+          <a:prstDash val="sysDot"/>
           <a:miter lim="800000"/>
         </a:ln>
       </xdr:spPr>
@@ -2042,13 +1942,13 @@
   <xdr:twoCellAnchor>
     <xdr:from>
       <xdr:col>2</xdr:col>
-      <xdr:colOff>317500</xdr:colOff>
+      <xdr:colOff>169545</xdr:colOff>
       <xdr:row>35</xdr:row>
       <xdr:rowOff>106045</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>3</xdr:col>
-      <xdr:colOff>106045</xdr:colOff>
+      <xdr:col>2</xdr:col>
+      <xdr:colOff>645795</xdr:colOff>
       <xdr:row>37</xdr:row>
       <xdr:rowOff>116205</xdr:rowOff>
     </xdr:to>
@@ -2061,8 +1961,8 @@
       </xdr:nvSpPr>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="1668145" y="5426710"/>
-          <a:ext cx="474345" cy="314960"/>
+          <a:off x="1520190" y="5426710"/>
+          <a:ext cx="476250" cy="314960"/>
         </a:xfrm>
         <a:prstGeom prst="rect"/>
         <a:noFill/>
@@ -2138,7 +2038,7 @@
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="1" name="図 1"/>
+        <xdr:cNvPr id="1" name="図 1" descr="xl/media/OImage2861529932.png"/>
         <xdr:cNvPicPr>
           <a:picLocks noChangeAspect="1"/>
         </xdr:cNvPicPr>
@@ -2191,7 +2091,7 @@
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="2" name="図 2"/>
+        <xdr:cNvPr id="2" name="図 2" descr="xl/media/OImage2852712973.png"/>
         <xdr:cNvPicPr>
           <a:picLocks noChangeAspect="1"/>
         </xdr:cNvPicPr>
@@ -2253,7 +2153,7 @@
               <a:alpha val="100000"/>
             </a:schemeClr>
           </a:solidFill>
-          <a:prstDash val="dot"/>
+          <a:prstDash val="sysDot"/>
           <a:miter lim="800000"/>
         </a:ln>
       </xdr:spPr>
@@ -2388,7 +2288,7 @@
               <a:alpha val="100000"/>
             </a:schemeClr>
           </a:solidFill>
-          <a:prstDash val="dot"/>
+          <a:prstDash val="sysDot"/>
           <a:miter lim="800000"/>
         </a:ln>
       </xdr:spPr>
@@ -2602,7 +2502,7 @@
               <a:alpha val="100000"/>
             </a:schemeClr>
           </a:solidFill>
-          <a:prstDash val="dot"/>
+          <a:prstDash val="sysDot"/>
           <a:miter lim="800000"/>
         </a:ln>
       </xdr:spPr>
@@ -2658,7 +2558,7 @@
               <a:alpha val="100000"/>
             </a:schemeClr>
           </a:solidFill>
-          <a:prstDash val="dot"/>
+          <a:prstDash val="sysDot"/>
           <a:miter lim="800000"/>
         </a:ln>
       </xdr:spPr>
@@ -2793,7 +2693,7 @@
               <a:alpha val="100000"/>
             </a:schemeClr>
           </a:solidFill>
-          <a:prstDash val="dot"/>
+          <a:prstDash val="sysDot"/>
           <a:miter lim="800000"/>
         </a:ln>
       </xdr:spPr>
@@ -2849,7 +2749,7 @@
               <a:alpha val="100000"/>
             </a:schemeClr>
           </a:solidFill>
-          <a:prstDash val="dot"/>
+          <a:prstDash val="sysDot"/>
           <a:miter lim="800000"/>
         </a:ln>
       </xdr:spPr>
@@ -3063,7 +2963,7 @@
               <a:alpha val="100000"/>
             </a:schemeClr>
           </a:solidFill>
-          <a:prstDash val="dot"/>
+          <a:prstDash val="sysDot"/>
           <a:miter lim="800000"/>
         </a:ln>
       </xdr:spPr>
@@ -3119,7 +3019,7 @@
               <a:alpha val="100000"/>
             </a:schemeClr>
           </a:solidFill>
-          <a:prstDash val="dot"/>
+          <a:prstDash val="sysDot"/>
           <a:miter lim="800000"/>
         </a:ln>
       </xdr:spPr>
@@ -3175,7 +3075,7 @@
               <a:alpha val="100000"/>
             </a:schemeClr>
           </a:solidFill>
-          <a:prstDash val="dot"/>
+          <a:prstDash val="sysDot"/>
           <a:miter lim="800000"/>
         </a:ln>
       </xdr:spPr>
@@ -3231,7 +3131,7 @@
               <a:alpha val="100000"/>
             </a:schemeClr>
           </a:solidFill>
-          <a:prstDash val="dot"/>
+          <a:prstDash val="sysDot"/>
           <a:miter lim="800000"/>
         </a:ln>
       </xdr:spPr>
@@ -3524,7 +3424,7 @@
               <a:alpha val="100000"/>
             </a:schemeClr>
           </a:solidFill>
-          <a:prstDash val="dot"/>
+          <a:prstDash val="sysDot"/>
           <a:miter lim="800000"/>
         </a:ln>
       </xdr:spPr>
@@ -3659,7 +3559,7 @@
               <a:alpha val="100000"/>
             </a:schemeClr>
           </a:solidFill>
-          <a:prstDash val="dot"/>
+          <a:prstDash val="sysDot"/>
           <a:miter lim="800000"/>
         </a:ln>
       </xdr:spPr>
@@ -3794,7 +3694,7 @@
               <a:alpha val="100000"/>
             </a:schemeClr>
           </a:solidFill>
-          <a:prstDash val="dot"/>
+          <a:prstDash val="sysDot"/>
           <a:miter lim="800000"/>
         </a:ln>
       </xdr:spPr>
@@ -4008,7 +3908,7 @@
               <a:alpha val="100000"/>
             </a:schemeClr>
           </a:solidFill>
-          <a:prstDash val="dot"/>
+          <a:prstDash val="sysDot"/>
           <a:miter lim="800000"/>
         </a:ln>
       </xdr:spPr>
@@ -4064,7 +3964,7 @@
               <a:alpha val="100000"/>
             </a:schemeClr>
           </a:solidFill>
-          <a:prstDash val="dot"/>
+          <a:prstDash val="sysDot"/>
           <a:miter lim="800000"/>
         </a:ln>
       </xdr:spPr>
@@ -4450,7 +4350,7 @@
   <dimension ref="A1"/>
   <sheetFormatPr defaultRowHeight="12.000000"/>
   <cols>
-    <col min="1" max="16384" style="3" width="9.00500011" customWidth="1" outlineLevel="0"/>
+    <col min="1" max="16384" style="2" width="9.00500011" customWidth="1" outlineLevel="0"/>
   </cols>
   <sheetData/>
   <phoneticPr fontId="1" type="noConversion"/>
